--- a/product_selector_out/STM32F303.xlsx
+++ b/product_selector_out/STM32F303.xlsx
@@ -1145,7 +1145,7 @@
       </c>
       <c r="AD12" s="4" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>115</t>
         </is>
       </c>
       <c r="AE12" s="4" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="R13" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="S13" s="4" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="AD13" s="4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>51</t>
         </is>
       </c>
       <c r="AE13" s="4" t="inlineStr">
@@ -6050,7 +6050,7 @@
       </c>
       <c r="AD27" s="4" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>115</t>
         </is>
       </c>
       <c r="AE27" s="4" t="inlineStr">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="R28" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="S28" s="4" t="inlineStr">
@@ -6377,7 +6377,7 @@
       </c>
       <c r="AD28" s="4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>51</t>
         </is>
       </c>
       <c r="AE28" s="4" t="inlineStr">

--- a/product_selector_out/STM32F303.xlsx
+++ b/product_selector_out/STM32F303.xlsx
@@ -4682,7 +4682,7 @@
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="AM23" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AN23" s="4" t="inlineStr">
@@ -4917,7 +4917,7 @@
       </c>
       <c r="BM23" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32f303c6.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32f303rd.pdf</t>
         </is>
       </c>
     </row>
@@ -6644,7 +6644,7 @@
       </c>
       <c r="R29" s="4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="S29" s="4" t="inlineStr">
@@ -6749,7 +6749,7 @@
       </c>
       <c r="AM29" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AN29" s="4" t="inlineStr">
@@ -6879,7 +6879,7 @@
       </c>
       <c r="BM29" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32f303c6.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32f303rd.pdf</t>
         </is>
       </c>
     </row>
@@ -7669,9 +7669,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM12" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN12" s="6" t="inlineStr">
@@ -7996,9 +7996,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM13" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN13" s="6" t="inlineStr">
@@ -8323,9 +8323,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM14" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN14" s="6" t="inlineStr">
@@ -10612,9 +10612,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM21" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN21" s="6" t="inlineStr">
@@ -11091,9 +11091,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
@@ -11101,249 +11101,249 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="F23" s="8" t="inlineStr">
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H23" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J23" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="L23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="M23" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="N23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="O23" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P23" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q23" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R23" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="T23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="U23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="V23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="W23" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X23" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y23" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z23" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AB23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AC23" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AD23" s="8" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="H23" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I23" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J23" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="K23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="L23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="M23" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="N23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="O23" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P23" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q23" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R23" s="7" t="inlineStr">
+      <c r="AE23" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF23" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AH23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AI23" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AK23" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AL23" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AM23" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AN23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AO23" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP23" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AQ23" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AR23" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AS23" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AT23" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU23" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV23" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW23" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AX23" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AY23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="BA23" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BB23" s="7" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="T23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="U23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="W23" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X23" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y23" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z23" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AB23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AC23" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AD23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AE23" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF23" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AH23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AI23" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AK23" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AL23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AM23" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AN23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AO23" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP23" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AQ23" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AR23" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AS23" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AT23" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU23" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV23" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AZ23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="BA23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="BB23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
         </is>
       </c>
       <c r="BC23" s="9" t="inlineStr">
@@ -12574,9 +12574,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM27" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN27" s="6" t="inlineStr">
@@ -12901,9 +12901,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM28" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN28" s="6" t="inlineStr">
@@ -13053,9 +13053,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
@@ -13063,249 +13063,249 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="F29" s="8" t="inlineStr">
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H29" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J29" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="K29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="L29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="M29" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="N29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="O29" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P29" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q29" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R29" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="T29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="U29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="V29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="W29" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X29" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y29" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z29" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AA29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AB29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AC29" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AD29" s="8" t="inlineStr">
         <is>
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="G29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="H29" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I29" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J29" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="K29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="L29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="M29" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="N29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="O29" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P29" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q29" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R29" s="7" t="inlineStr">
+      <c r="AE29" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF29" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AH29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AI29" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AJ29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AK29" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AL29" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AM29" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AN29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AO29" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP29" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AQ29" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AR29" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AS29" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AT29" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU29" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV29" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW29" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AX29" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AY29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="BA29" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BB29" s="7" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="T29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="U29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="W29" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X29" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y29" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z29" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AA29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AB29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AC29" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AD29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AE29" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF29" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AH29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AI29" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AJ29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AK29" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AL29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AM29" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AN29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AO29" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP29" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AQ29" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AR29" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AS29" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AT29" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU29" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV29" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AZ29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="BA29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="BB29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
         </is>
       </c>
       <c r="BC29" s="9" t="inlineStr">
@@ -13902,7 +13902,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -13912,7 +13912,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F303xD/E family device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
@@ -13924,7 +13924,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -13934,7 +13934,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
@@ -14166,7 +14166,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -14176,7 +14176,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F303xD/E family device features and peripheral counts lists LQFP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
@@ -14188,7 +14188,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Ambient operating temperature: - 40 to 85 °C / - 40 to 105 °C Junction temperature: - 40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>

--- a/product_selector_out/STM32F303.xlsx
+++ b/product_selector_out/STM32F303.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM29"/>
+  <dimension ref="A1:BN29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.51953125" customWidth="1" min="1" max="1"/>
@@ -573,7 +573,8 @@
     <col width="21.765625" customWidth="1" min="62" max="62"/>
     <col width="18" customWidth="1" min="63" max="63"/>
     <col width="18" customWidth="1" min="64" max="64"/>
-    <col width="52" customWidth="1" min="65" max="65"/>
+    <col width="18" customWidth="1" min="65" max="65"/>
+    <col width="52" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -901,6 +902,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -996,6 +1002,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1320,6 +1327,11 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f303rd.pdf</t>
         </is>
       </c>
@@ -1647,6 +1659,11 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f303rd.pdf</t>
         </is>
       </c>
@@ -1974,6 +1991,11 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f303rd.pdf</t>
         </is>
       </c>
@@ -2301,6 +2323,11 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f303c6.pdf</t>
         </is>
       </c>
@@ -2628,6 +2655,11 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f303cb.pdf</t>
         </is>
       </c>
@@ -2955,6 +2987,11 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f303c6.pdf</t>
         </is>
       </c>
@@ -3282,6 +3319,11 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f303cb.pdf</t>
         </is>
       </c>
@@ -3609,6 +3651,11 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f303cb.pdf</t>
         </is>
       </c>
@@ -3936,6 +3983,11 @@
       </c>
       <c r="BM20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f303cb.pdf</t>
         </is>
       </c>
@@ -4263,6 +4315,11 @@
       </c>
       <c r="BM21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f303rd.pdf</t>
         </is>
       </c>
@@ -4590,6 +4647,11 @@
       </c>
       <c r="BM22" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f303cb.pdf</t>
         </is>
       </c>
@@ -4917,6 +4979,11 @@
       </c>
       <c r="BM23" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f303rd.pdf</t>
         </is>
       </c>
@@ -5244,6 +5311,11 @@
       </c>
       <c r="BM24" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f303cb.pdf</t>
         </is>
       </c>
@@ -5571,6 +5643,11 @@
       </c>
       <c r="BM25" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN25" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f303c6.pdf</t>
         </is>
       </c>
@@ -5898,6 +5975,11 @@
       </c>
       <c r="BM26" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN26" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f303c6.pdf</t>
         </is>
       </c>
@@ -6225,6 +6307,11 @@
       </c>
       <c r="BM27" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN27" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f303rd.pdf</t>
         </is>
       </c>
@@ -6552,6 +6639,11 @@
       </c>
       <c r="BM28" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN28" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f303rd.pdf</t>
         </is>
       </c>
@@ -6879,12 +6971,17 @@
       </c>
       <c r="BM29" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN29" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f303rd.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="64">
+  <mergeCells count="65">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -6905,16 +7002,14 @@
     <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="BG10:BG11"/>
     <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="A1:BM8"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="AT10:AT11"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="AV10:AV11"/>
-    <mergeCell ref="A9:BM9"/>
     <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -6927,6 +7022,7 @@
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
     <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
@@ -6946,7 +7042,9 @@
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="AG10:AG11"/>
     <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A9:BN9"/>
     <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A1:BN8"/>
     <mergeCell ref="T10:T11"/>
     <mergeCell ref="J10:J11"/>
   </mergeCells>
@@ -6981,7 +7079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM29"/>
+  <dimension ref="A1:BN29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7049,6 +7147,7 @@
     <col width="16" customWidth="1" min="63" max="63"/>
     <col width="16" customWidth="1" min="64" max="64"/>
     <col width="16" customWidth="1" min="65" max="65"/>
+    <col width="16" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7382,6 +7481,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -7477,6 +7581,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -7799,7 +7904,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
+      <c r="BM12" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8126,7 +8236,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="6" t="inlineStr">
+      <c r="BM13" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8453,7 +8568,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
+      <c r="BM14" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8780,7 +8900,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
+      <c r="BM15" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9107,7 +9232,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
+      <c r="BM16" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9434,7 +9564,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
+      <c r="BM17" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9761,7 +9896,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="6" t="inlineStr">
+      <c r="BM18" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10088,7 +10228,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="6" t="inlineStr">
+      <c r="BM19" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10415,7 +10560,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM20" s="6" t="inlineStr">
+      <c r="BM20" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10742,7 +10892,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM21" s="6" t="inlineStr">
+      <c r="BM21" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11069,7 +11224,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM22" s="6" t="inlineStr">
+      <c r="BM22" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11396,7 +11556,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM23" s="6" t="inlineStr">
+      <c r="BM23" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11723,7 +11888,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM24" s="6" t="inlineStr">
+      <c r="BM24" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12050,7 +12220,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM25" s="6" t="inlineStr">
+      <c r="BM25" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN25" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12377,7 +12552,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM26" s="6" t="inlineStr">
+      <c r="BM26" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN26" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12704,7 +12884,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM27" s="6" t="inlineStr">
+      <c r="BM27" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN27" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13031,7 +13216,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM28" s="6" t="inlineStr">
+      <c r="BM28" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN28" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13358,7 +13548,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM29" s="6" t="inlineStr">
+      <c r="BM29" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN29" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13366,8 +13561,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BM9"/>
-    <mergeCell ref="A1:BM8"/>
+    <mergeCell ref="A9:BN9"/>
+    <mergeCell ref="A1:BN8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
